--- a/artfynd/A 7234-2024 artfynd.xlsx
+++ b/artfynd/A 7234-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136544791</v>
       </c>
       <c r="B3" t="n">
-        <v>106358</v>
+        <v>106361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533788</v>
       </c>
       <c r="B4" t="n">
-        <v>103025</v>
+        <v>103028</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136535028</v>
       </c>
       <c r="B5" t="n">
-        <v>103025</v>
+        <v>103028</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537792</v>
       </c>
       <c r="B6" t="n">
-        <v>103025</v>
+        <v>103028</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 7234-2024 artfynd.xlsx
+++ b/artfynd/A 7234-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136544791</v>
       </c>
       <c r="B3" t="n">
-        <v>106361</v>
+        <v>106362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533788</v>
       </c>
       <c r="B4" t="n">
-        <v>103028</v>
+        <v>103029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136535028</v>
       </c>
       <c r="B5" t="n">
-        <v>103028</v>
+        <v>103029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537792</v>
       </c>
       <c r="B6" t="n">
-        <v>103028</v>
+        <v>103029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 7234-2024 artfynd.xlsx
+++ b/artfynd/A 7234-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136534766</v>
       </c>
       <c r="B2" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136544791</v>
       </c>
       <c r="B3" t="n">
-        <v>106362</v>
+        <v>106367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533788</v>
       </c>
       <c r="B4" t="n">
-        <v>103029</v>
+        <v>103034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136535028</v>
       </c>
       <c r="B5" t="n">
-        <v>103029</v>
+        <v>103034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537792</v>
       </c>
       <c r="B6" t="n">
-        <v>103029</v>
+        <v>103034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 7234-2024 artfynd.xlsx
+++ b/artfynd/A 7234-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136544791</v>
       </c>
       <c r="B3" t="n">
-        <v>106367</v>
+        <v>106369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533788</v>
       </c>
       <c r="B4" t="n">
-        <v>103034</v>
+        <v>103036</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136535028</v>
       </c>
       <c r="B5" t="n">
-        <v>103034</v>
+        <v>103036</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537792</v>
       </c>
       <c r="B6" t="n">
-        <v>103034</v>
+        <v>103036</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 7234-2024 artfynd.xlsx
+++ b/artfynd/A 7234-2024 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist</t>
+          <t>Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -789,7 +789,7 @@
         <v>136544791</v>
       </c>
       <c r="B3" t="n">
-        <v>106369</v>
+        <v>106375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533788</v>
       </c>
       <c r="B4" t="n">
-        <v>103036</v>
+        <v>103042</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136535028</v>
       </c>
       <c r="B5" t="n">
-        <v>103036</v>
+        <v>103042</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537792</v>
       </c>
       <c r="B6" t="n">
-        <v>103036</v>
+        <v>103042</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 7234-2024 artfynd.xlsx
+++ b/artfynd/A 7234-2024 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -789,7 +789,7 @@
         <v>136544791</v>
       </c>
       <c r="B3" t="n">
-        <v>106375</v>
+        <v>106377</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533788</v>
       </c>
       <c r="B4" t="n">
-        <v>103042</v>
+        <v>103044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136535028</v>
       </c>
       <c r="B5" t="n">
-        <v>103042</v>
+        <v>103044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537792</v>
       </c>
       <c r="B6" t="n">
-        <v>103042</v>
+        <v>103044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 7234-2024 artfynd.xlsx
+++ b/artfynd/A 7234-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136544791</v>
       </c>
       <c r="B3" t="n">
-        <v>106377</v>
+        <v>106378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533788</v>
       </c>
       <c r="B4" t="n">
-        <v>103044</v>
+        <v>103045</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136535028</v>
       </c>
       <c r="B5" t="n">
-        <v>103044</v>
+        <v>103045</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537792</v>
       </c>
       <c r="B6" t="n">
-        <v>103044</v>
+        <v>103045</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 7234-2024 artfynd.xlsx
+++ b/artfynd/A 7234-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136544791</v>
       </c>
       <c r="B3" t="n">
-        <v>106378</v>
+        <v>106384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533788</v>
       </c>
       <c r="B4" t="n">
-        <v>103045</v>
+        <v>103051</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136535028</v>
       </c>
       <c r="B5" t="n">
-        <v>103045</v>
+        <v>103051</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537792</v>
       </c>
       <c r="B6" t="n">
-        <v>103045</v>
+        <v>103051</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 7234-2024 artfynd.xlsx
+++ b/artfynd/A 7234-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136544791</v>
       </c>
       <c r="B3" t="n">
-        <v>106384</v>
+        <v>106388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533788</v>
       </c>
       <c r="B4" t="n">
-        <v>103051</v>
+        <v>103055</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136535028</v>
       </c>
       <c r="B5" t="n">
-        <v>103051</v>
+        <v>103055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537792</v>
       </c>
       <c r="B6" t="n">
-        <v>103051</v>
+        <v>103055</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 7234-2024 artfynd.xlsx
+++ b/artfynd/A 7234-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136544791</v>
       </c>
       <c r="B3" t="n">
-        <v>106388</v>
+        <v>106390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533788</v>
       </c>
       <c r="B4" t="n">
-        <v>103055</v>
+        <v>103057</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136535028</v>
       </c>
       <c r="B5" t="n">
-        <v>103055</v>
+        <v>103057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537792</v>
       </c>
       <c r="B6" t="n">
-        <v>103055</v>
+        <v>103057</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 7234-2024 artfynd.xlsx
+++ b/artfynd/A 7234-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136544791</v>
       </c>
       <c r="B3" t="n">
-        <v>106390</v>
+        <v>106392</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533788</v>
       </c>
       <c r="B4" t="n">
-        <v>103057</v>
+        <v>103059</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136535028</v>
       </c>
       <c r="B5" t="n">
-        <v>103057</v>
+        <v>103059</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537792</v>
       </c>
       <c r="B6" t="n">
-        <v>103057</v>
+        <v>103059</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 7234-2024 artfynd.xlsx
+++ b/artfynd/A 7234-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136534766</v>
       </c>
       <c r="B2" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136544791</v>
       </c>
       <c r="B3" t="n">
-        <v>106392</v>
+        <v>106405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533788</v>
       </c>
       <c r="B4" t="n">
-        <v>103059</v>
+        <v>103072</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136535028</v>
       </c>
       <c r="B5" t="n">
-        <v>103059</v>
+        <v>103072</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537792</v>
       </c>
       <c r="B6" t="n">
-        <v>103059</v>
+        <v>103072</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 7234-2024 artfynd.xlsx
+++ b/artfynd/A 7234-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136534766</v>
       </c>
       <c r="B2" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136544791</v>
       </c>
       <c r="B3" t="n">
-        <v>106405</v>
+        <v>106407</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533788</v>
       </c>
       <c r="B4" t="n">
-        <v>103072</v>
+        <v>103074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136535028</v>
       </c>
       <c r="B5" t="n">
-        <v>103072</v>
+        <v>103074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537792</v>
       </c>
       <c r="B6" t="n">
-        <v>103072</v>
+        <v>103074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
